--- a/予実管理_高松二丁目_v1.xlsx
+++ b/予実管理_高松二丁目_v1.xlsx
@@ -540,12 +540,12 @@
           <t>手付金</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>1000000</v>
+      <c r="C4" s="3" t="n">
+        <v>2000000</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>仮置き。契約書ドラフトで確定後修正</t>
+          <t>各100万×売主2系統(合意済み)。決済時に代金充当</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
           <t>諸費用合計</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>2500000</v>
+      <c r="C5" s="3" t="n">
+        <v>2487000</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>仮置き。『諸費用明細_高松二丁目』の合計を転記</t>
+          <t>諸費用明細の確定値(司法書士99.5万・火災保険19万見込み込み)</t>
         </is>
       </c>
     </row>
@@ -615,27 +615,27 @@
           <t>満室想定賃料/月（アーバンキューブ）</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>500000</v>
+      <c r="C9" s="3" t="n">
+        <v>336000</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>仮置き。レントロールで確定（大学生協管理）</t>
+          <t>レントロール実数: 8戸×42,000円(賃料4万+共益2千)満室</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>満室想定賃料/月（花みずき3棟）</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>180000</v>
+          <t>現況賃料/月（花みずき3棟・2/3入居）</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>108300</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>仮置き。レントロールで確定（トラステン管理）</t>
+          <t>レントロール実数: 1号63,300+2号45,000。3号空室(再募集45,000)</t>
         </is>
       </c>
     </row>

--- a/予実管理_高松二丁目_v1.xlsx
+++ b/予実管理_高松二丁目_v1.xlsx
@@ -541,11 +541,11 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>各100万×売主2系統(合意済み)。決済時に代金充当</t>
+          <t>各10万×2契約(確定)</t>
         </is>
       </c>
     </row>
@@ -556,11 +556,11 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2487000</v>
+        <v>6628948</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>諸費用明細の確定値(司法書士99.5万・火災保険19万見込み込み)</t>
+          <t>諸費用明細の確定値(保証料427.8万含む)</t>
         </is>
       </c>
     </row>
@@ -571,11 +571,11 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37000000</v>
+        <v>43200000</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>岩手銀行（根抵当極度額6,000万円）</t>
+          <t>岩銀2本立て・諸費用込み融資(確定)</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
           <t>金利（年率）</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>0.015</v>
+      <c r="C7" s="7" t="n">
+        <v>0.0275</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>仮置き1.5%。西原様確認中</t>
+          <t>確定: 変動2.750%(短プラ連動)</t>
         </is>
       </c>
     </row>
@@ -600,12 +600,12 @@
           <t>融資期間（年）</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>25</v>
+      <c r="C8" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>仮置き。西原様確認中</t>
+          <t>確定: 240ヶ月</t>
         </is>
       </c>
     </row>
